--- a/Чертежи и спеки шкафов/Чертежи/Актуальные/3.Сервер/Спецификация Серверный шкаф.xlsx
+++ b/Чертежи и спеки шкафов/Чертежи/Актуальные/3.Сервер/Спецификация Серверный шкаф.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF190F4A-E877-4A1E-AA30-DFE575E53891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35002A94-D31E-436F-8012-B88006426B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="78">
   <si>
     <t>Обозн</t>
   </si>
@@ -256,6 +256,15 @@
   </si>
   <si>
     <t>N2010-IGMSX850-055</t>
+  </si>
+  <si>
+    <t>Cервер точного времени по стандарту NTP</t>
+  </si>
+  <si>
+    <t>RTNTP-1A</t>
+  </si>
+  <si>
+    <t>ООО «Р-Тех»</t>
   </si>
 </sst>
 </file>
@@ -418,9 +427,6 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -428,6 +434,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -808,7 +817,7 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
       <c r="F3" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="14"/>
       <c r="H3" s="15"/>
@@ -1030,7 +1039,7 @@
       <c r="F12" s="2">
         <v>1</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="19"/>
       <c r="H12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1053,7 +1062,7 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="18">
         <v>106619.48</v>
       </c>
       <c r="H13" s="13">
@@ -1075,10 +1084,10 @@
       <c r="E14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="20">
         <v>4</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="18">
         <v>5076.8999999999996</v>
       </c>
       <c r="H14" s="13">
@@ -1103,7 +1112,7 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="19"/>
       <c r="H15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -1151,7 +1160,7 @@
       <c r="F17" s="2">
         <v>6</v>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="18">
         <v>1176.69</v>
       </c>
       <c r="H17" s="13">
@@ -1173,10 +1182,10 @@
       <c r="E18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="20">
         <v>1</v>
       </c>
-      <c r="G18" s="19">
+      <c r="G18" s="18">
         <v>458.33</v>
       </c>
       <c r="H18" s="13">
@@ -1201,7 +1210,7 @@
       <c r="F19" s="2">
         <v>4</v>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="18">
         <v>213.21</v>
       </c>
       <c r="H19" s="13">
@@ -1226,7 +1235,7 @@
       <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="18">
         <v>1091.67</v>
       </c>
       <c r="H20" s="13">
@@ -1251,7 +1260,7 @@
       <c r="F21" s="2">
         <v>2</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="18">
         <v>56066.67</v>
       </c>
       <c r="H21" s="13">
@@ -1276,7 +1285,7 @@
       <c r="F22" s="2">
         <v>4</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="18">
         <v>34533.33</v>
       </c>
       <c r="H22" s="13">
@@ -1301,7 +1310,7 @@
       <c r="F23" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="18">
         <v>430.07</v>
       </c>
       <c r="H23" s="13">
@@ -1326,7 +1335,7 @@
       <c r="F24" s="2">
         <v>7</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="18">
         <v>37.53</v>
       </c>
       <c r="H24" s="13">
@@ -1347,7 +1356,7 @@
       <c r="F25" s="2">
         <v>10</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="18">
         <v>33.33</v>
       </c>
       <c r="H25" s="13">
@@ -1372,7 +1381,7 @@
       <c r="F26" s="2">
         <v>2</v>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="18">
         <v>909.33</v>
       </c>
       <c r="H26" s="13">
@@ -1397,7 +1406,7 @@
       <c r="F27" s="2">
         <v>2</v>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="18">
         <v>228</v>
       </c>
       <c r="H27" s="13">
@@ -1422,7 +1431,7 @@
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="18">
         <v>296.88</v>
       </c>
       <c r="H28" s="13">
@@ -1470,14 +1479,14 @@
         <v>7</v>
       </c>
       <c r="F30" s="2">
-        <v>6</v>
-      </c>
-      <c r="G30" s="19">
+        <v>2</v>
+      </c>
+      <c r="G30" s="18">
         <v>5517.97</v>
       </c>
       <c r="H30" s="13">
         <f t="shared" si="2"/>
-        <v>33107.82</v>
+        <v>11035.94</v>
       </c>
     </row>
     <row r="31" spans="1:8" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1497,7 +1506,7 @@
       <c r="F31" s="2">
         <v>2</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="18">
         <v>7555.21</v>
       </c>
       <c r="H31" s="13">
@@ -1505,14 +1514,38 @@
         <v>15110.42</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2">
+        <v>2</v>
+      </c>
+      <c r="G32" s="18">
+        <v>54780</v>
+      </c>
+      <c r="H32" s="13">
+        <f t="shared" ref="H32" si="3">G32*F32</f>
+        <v>109560</v>
+      </c>
+    </row>
     <row r="33" spans="7:8" s="1" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G33" s="18" t="s">
+      <c r="G33" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="H33" s="18">
-        <f>SUM(H4:H31)</f>
-        <v>889771.47</v>
+      <c r="H33" s="17">
+        <f>SUM(H4:H32)</f>
+        <v>977259.59</v>
       </c>
     </row>
     <row r="34" spans="7:8" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
